--- a/DHD Pilot Study with Lang Specific Prompts/DHD_English.xlsx
+++ b/DHD Pilot Study with Lang Specific Prompts/DHD_English.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,11 +446,6 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Offensiveness</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>Humor Attribute</t>
         </is>
       </c>
@@ -467,12 +462,9 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Irony</t>
         </is>
@@ -490,12 +482,9 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Wordplay</t>
         </is>
@@ -513,12 +502,9 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Absurdity</t>
         </is>
@@ -536,12 +522,9 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Social Commentary</t>
         </is>
@@ -559,12 +542,9 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Irony</t>
         </is>
@@ -582,12 +562,9 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Dark Humor</t>
         </is>
@@ -605,12 +582,9 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Social Commentary</t>
         </is>
@@ -628,12 +602,9 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Irony</t>
         </is>
@@ -651,12 +622,9 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Wordplay</t>
         </is>
@@ -674,12 +642,9 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Dark Humor</t>
         </is>
@@ -697,12 +662,9 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>Social Commentary</t>
         </is>
@@ -720,12 +682,9 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Irony</t>
         </is>
@@ -743,12 +702,9 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Dark Humor</t>
         </is>
@@ -766,12 +722,9 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Absurdity</t>
         </is>
@@ -789,12 +742,9 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Social Commentary</t>
         </is>
@@ -812,12 +762,9 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Irony</t>
         </is>
@@ -835,12 +782,9 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Wordplay</t>
         </is>
@@ -858,12 +802,9 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
-      </c>
-      <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Irony</t>
         </is>
@@ -881,12 +822,9 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
-      </c>
-      <c r="D20" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Absurdity</t>
         </is>
@@ -904,12 +842,9 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Social Commentary</t>
         </is>
@@ -927,12 +862,9 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>Wordplay</t>
         </is>
@@ -950,12 +882,9 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
-      </c>
-      <c r="D23" t="n">
         <v>1</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Absurdity</t>
         </is>
@@ -973,12 +902,9 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" t="n">
-        <v>3</v>
-      </c>
-      <c r="E24" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Social Commentary</t>
         </is>
@@ -996,12 +922,9 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
-      </c>
-      <c r="D25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E25" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Social Commentary</t>
         </is>
@@ -1019,12 +942,9 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
-      </c>
-      <c r="D26" t="n">
-        <v>3</v>
-      </c>
-      <c r="E26" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Social Commentary</t>
         </is>
@@ -1042,12 +962,9 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
-      </c>
-      <c r="D27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Irony</t>
         </is>
@@ -1065,12 +982,9 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>Absurdity</t>
         </is>
@@ -1088,12 +1002,9 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
-      </c>
-      <c r="D29" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Dark Humor</t>
         </is>
@@ -1111,12 +1022,9 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
-      </c>
-      <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Absurdity</t>
         </is>
@@ -1134,12 +1042,9 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Irony</t>
         </is>
@@ -1157,12 +1062,9 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Absurdity</t>
         </is>
@@ -1180,12 +1082,9 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
-      </c>
-      <c r="D33" t="n">
-        <v>3</v>
-      </c>
-      <c r="E33" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>Dark Humor</t>
         </is>
@@ -1203,12 +1102,9 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Social Commentary</t>
         </is>
@@ -1226,12 +1122,9 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>Irony</t>
         </is>
@@ -1249,12 +1142,9 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
-      </c>
-      <c r="D36" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>Absurdity</t>
         </is>
@@ -1272,12 +1162,9 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
-      </c>
-      <c r="D37" t="n">
-        <v>4</v>
-      </c>
-      <c r="E37" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Dark Humor</t>
         </is>
@@ -1295,12 +1182,9 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>Social Commentary</t>
         </is>
@@ -1318,12 +1202,9 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Irony</t>
         </is>
@@ -1341,12 +1222,9 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
-      </c>
-      <c r="D40" t="n">
-        <v>3</v>
-      </c>
-      <c r="E40" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>Social Commentary</t>
         </is>
@@ -1364,12 +1242,9 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
-      </c>
-      <c r="D41" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>Social Commentary</t>
         </is>
@@ -1387,12 +1262,9 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
-      </c>
-      <c r="D42" t="n">
         <v>1</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Absurdity</t>
         </is>
@@ -1410,12 +1282,9 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
-      </c>
-      <c r="D43" t="n">
-        <v>3</v>
-      </c>
-      <c r="E43" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>Social Commentary</t>
         </is>
@@ -1433,12 +1302,9 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
-      </c>
-      <c r="D44" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>Dark Humor</t>
         </is>
@@ -1456,12 +1322,9 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
-      </c>
-      <c r="D45" t="n">
         <v>1</v>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Absurdity</t>
         </is>
@@ -1479,12 +1342,9 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
-      </c>
-      <c r="D46" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>Social Commentary</t>
         </is>
@@ -1502,12 +1362,9 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E47" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>Irony</t>
         </is>
@@ -1525,12 +1382,9 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
-      </c>
-      <c r="D48" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>Dark Humor</t>
         </is>
@@ -1548,12 +1402,9 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
-      </c>
-      <c r="D49" t="n">
-        <v>2</v>
-      </c>
-      <c r="E49" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>Social Commentary</t>
         </is>
@@ -1571,12 +1422,9 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
-      </c>
-      <c r="D50" t="n">
-        <v>3</v>
-      </c>
-      <c r="E50" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>Social Commentary</t>
         </is>
@@ -1594,12 +1442,9 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
-      </c>
-      <c r="D51" t="n">
-        <v>3</v>
-      </c>
-      <c r="E51" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>Social Commentary</t>
         </is>
